--- a/Documentos/MIA — Serie histórica 2020-2026.xlsx
+++ b/Documentos/MIA — Serie histórica 2020-2026.xlsx
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,37 +430,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>periodo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MIA Núcleo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ejecutivo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Legislativo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Judicial</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Prensa</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Banco Central</t>
         </is>
@@ -2173,37 +2161,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MIA Núcleo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ejecutivo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Legislativo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Judicial</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Prensa</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Banco Central</t>
         </is>
@@ -2623,57 +2611,57 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>periodo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ejecutivo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Legislativo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Judicial</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Prensa</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Banco Central</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>cobertura_vars</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>actualizado</t>
         </is>
@@ -3864,34 +3852,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>54.52</v>
+        <v>54.8</v>
       </c>
       <c r="C33" t="n">
-        <v>50.81</v>
+        <v>51.44</v>
       </c>
       <c r="D33" t="n">
-        <v>46.67</v>
+        <v>48.04</v>
       </c>
       <c r="E33" t="n">
-        <v>44.95</v>
+        <v>45.18</v>
       </c>
       <c r="F33" t="n">
-        <v>71.51000000000001</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>68.15000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="H33" t="n">
         <v>18</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>cerrado</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-19 10:04</t>
+          <t>2026-09-17 15:24</t>
         </is>
       </c>
     </row>
@@ -3931,97 +3919,97 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>periodo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DNU vs Leyes</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Discrecionalidad presup.</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Transparencia (AIP)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ATN (federalismo)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Eficacia de Control</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Calidad Normativa</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Costo del Legislativo</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Desempeño de la Corte</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Cobertura Judicial</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Escrutinio Abierto</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Pauta Publicitaria</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Causas contra periodistas</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Medios estatales</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Acceso de la prensa</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Financiamiento al Tesoro</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Letras intransferibles</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Designación Pdte. BCRA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Respeto Carta Orgánica</t>
         </is>
@@ -5921,13 +5909,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="C33" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>65.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E33" t="n">
         <v>81.3</v>
@@ -5936,16 +5924,16 @@
         <v>20.9</v>
       </c>
       <c r="G33" t="n">
-        <v>69.5</v>
+        <v>70</v>
       </c>
       <c r="H33" t="n">
-        <v>73.5</v>
+        <v>83.3</v>
       </c>
       <c r="I33" t="n">
         <v>30</v>
       </c>
       <c r="J33" t="n">
-        <v>67.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="K33" t="n">
         <v>100</v>
@@ -5957,16 +5945,16 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>71.8</v>
+        <v>71.7</v>
       </c>
       <c r="O33" t="n">
-        <v>64.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="P33" t="n">
-        <v>87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>68.2</v>
+        <v>62.3</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -5994,12 +5982,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Serie</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>

--- a/Documentos/MIA — Serie histórica 2020-2026.xlsx
+++ b/Documentos/MIA — Serie histórica 2020-2026.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -473,14 +473,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.98</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+        <v>69.06999999999999</v>
+      </c>
+      <c r="C2" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="D2" t="n">
+        <v>93.67</v>
+      </c>
+      <c r="E2" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="F2" t="n">
+        <v>58.9</v>
+      </c>
       <c r="G2" t="n">
-        <v>21.98</v>
+        <v>35.65</v>
       </c>
     </row>
     <row r="3">
@@ -490,14 +498,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+        <v>66.94</v>
+      </c>
+      <c r="C3" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="E3" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="F3" t="n">
+        <v>59.77</v>
+      </c>
       <c r="G3" t="n">
-        <v>18.99</v>
+        <v>32.76</v>
       </c>
     </row>
     <row r="4">
@@ -507,14 +523,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+        <v>64.58</v>
+      </c>
+      <c r="C4" t="n">
+        <v>69.16</v>
+      </c>
+      <c r="D4" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="E4" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>60.63</v>
+      </c>
       <c r="G4" t="n">
-        <v>18.15</v>
+        <v>30.94</v>
       </c>
     </row>
     <row r="5">
@@ -524,14 +548,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.09</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+        <v>61.91</v>
+      </c>
+      <c r="C5" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="D5" t="n">
+        <v>91.78</v>
+      </c>
+      <c r="E5" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="F5" t="n">
+        <v>61.5</v>
+      </c>
       <c r="G5" t="n">
-        <v>17.09</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="6">
@@ -541,14 +573,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+        <v>59.03</v>
+      </c>
+      <c r="C6" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="D6" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="E6" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="F6" t="n">
+        <v>62.36</v>
+      </c>
       <c r="G6" t="n">
-        <v>16.17</v>
+        <v>25.91</v>
       </c>
     </row>
     <row r="7">
@@ -558,14 +598,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+        <v>56.01</v>
+      </c>
+      <c r="C7" t="n">
+        <v>46.36</v>
+      </c>
+      <c r="D7" t="n">
+        <v>88.01000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="F7" t="n">
+        <v>63.23</v>
+      </c>
       <c r="G7" t="n">
-        <v>15.25</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="8">
@@ -575,14 +623,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.31</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+        <v>52.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="E8" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="F8" t="n">
+        <v>64.09</v>
+      </c>
       <c r="G8" t="n">
-        <v>14.31</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="9">
@@ -592,14 +648,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+        <v>49.73</v>
+      </c>
+      <c r="C9" t="n">
+        <v>30.37</v>
+      </c>
+      <c r="D9" t="n">
+        <v>84.08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="F9" t="n">
+        <v>64.95</v>
+      </c>
       <c r="G9" t="n">
-        <v>12.71</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="10">
@@ -609,14 +673,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+        <v>46.94</v>
+      </c>
+      <c r="C10" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="D10" t="n">
+        <v>80.44</v>
+      </c>
+      <c r="E10" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="F10" t="n">
+        <v>65.81999999999999</v>
+      </c>
       <c r="G10" t="n">
-        <v>10.96</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="11">
@@ -626,14 +698,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+        <v>45.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="D11" t="n">
+        <v>77.23999999999999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="F11" t="n">
+        <v>66.68000000000001</v>
+      </c>
       <c r="G11" t="n">
-        <v>9.1</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="12">
@@ -643,14 +723,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+        <v>43.6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="D12" t="n">
+        <v>74.98</v>
+      </c>
+      <c r="E12" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="F12" t="n">
+        <v>67.55</v>
+      </c>
       <c r="G12" t="n">
-        <v>7.15</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -660,14 +748,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+        <v>42.54</v>
+      </c>
+      <c r="C13" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="D13" t="n">
+        <v>72.87</v>
+      </c>
+      <c r="E13" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="F13" t="n">
+        <v>68.41</v>
+      </c>
       <c r="G13" t="n">
-        <v>6.89</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="14">
@@ -677,14 +773,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+        <v>41.46</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="D14" t="n">
+        <v>71</v>
+      </c>
+      <c r="E14" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="F14" t="n">
+        <v>67.63</v>
+      </c>
       <c r="G14" t="n">
-        <v>6.65</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="15">
@@ -694,14 +798,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+        <v>40.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="D15" t="n">
+        <v>68.91</v>
+      </c>
+      <c r="E15" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="F15" t="n">
+        <v>66.84999999999999</v>
+      </c>
       <c r="G15" t="n">
-        <v>6.39</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -711,14 +823,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+        <v>39.95</v>
+      </c>
+      <c r="C16" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="D16" t="n">
+        <v>67.17</v>
+      </c>
+      <c r="E16" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="F16" t="n">
+        <v>66.06999999999999</v>
+      </c>
       <c r="G16" t="n">
-        <v>6.13</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="17">
@@ -728,14 +848,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+        <v>39.78</v>
+      </c>
+      <c r="C17" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="D17" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="F17" t="n">
+        <v>65.29000000000001</v>
+      </c>
       <c r="G17" t="n">
-        <v>5.87</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -745,14 +873,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+        <v>40.17</v>
+      </c>
+      <c r="C18" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="D18" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="E18" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="F18" t="n">
+        <v>64.51000000000001</v>
+      </c>
       <c r="G18" t="n">
-        <v>5.72</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="19">
@@ -762,14 +898,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+        <v>41.37</v>
+      </c>
+      <c r="C19" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>64.63</v>
+      </c>
+      <c r="E19" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="F19" t="n">
+        <v>63.72</v>
+      </c>
       <c r="G19" t="n">
-        <v>5.63</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="20">
@@ -779,14 +923,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+        <v>42.98</v>
+      </c>
+      <c r="C20" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="D20" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="E20" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="F20" t="n">
+        <v>62.94</v>
+      </c>
       <c r="G20" t="n">
-        <v>5.5</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="21">
@@ -796,14 +948,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+        <v>44.56</v>
+      </c>
+      <c r="C21" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="D21" t="n">
+        <v>63.46</v>
+      </c>
+      <c r="E21" t="n">
+        <v>60.49</v>
+      </c>
+      <c r="F21" t="n">
+        <v>62.16</v>
+      </c>
       <c r="G21" t="n">
-        <v>5.37</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="22">
@@ -813,14 +973,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+        <v>46.43</v>
+      </c>
+      <c r="C22" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="D22" t="n">
+        <v>63.79</v>
+      </c>
+      <c r="E22" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="F22" t="n">
+        <v>61.38</v>
+      </c>
       <c r="G22" t="n">
-        <v>4.88</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="23">
@@ -830,14 +998,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+        <v>47.98</v>
+      </c>
+      <c r="C23" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="D23" t="n">
+        <v>63.45</v>
+      </c>
+      <c r="E23" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="F23" t="n">
+        <v>60.6</v>
+      </c>
       <c r="G23" t="n">
-        <v>4.63</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="24">
@@ -847,14 +1023,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+        <v>49.37</v>
+      </c>
+      <c r="C24" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>62.18</v>
+      </c>
+      <c r="E24" t="n">
+        <v>63.32</v>
+      </c>
+      <c r="F24" t="n">
+        <v>59.82</v>
+      </c>
       <c r="G24" t="n">
-        <v>4.47</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="25">
@@ -864,14 +1048,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+        <v>50.43</v>
+      </c>
+      <c r="C25" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="D25" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="E25" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="F25" t="n">
+        <v>59.04</v>
+      </c>
       <c r="G25" t="n">
-        <v>4.43</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="26">
@@ -881,14 +1073,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+        <v>50.85</v>
+      </c>
+      <c r="C26" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>60.66</v>
+      </c>
+      <c r="E26" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>58.62</v>
+      </c>
       <c r="G26" t="n">
-        <v>4.34</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="27">
@@ -898,14 +1098,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+        <v>51.28</v>
+      </c>
+      <c r="C27" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="D27" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="E27" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="F27" t="n">
+        <v>58.2</v>
+      </c>
       <c r="G27" t="n">
-        <v>4.21</v>
+        <v>15.47</v>
       </c>
     </row>
     <row r="28">
@@ -915,14 +1123,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+        <v>51.8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>51.73</v>
+      </c>
+      <c r="D28" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="E28" t="n">
+        <v>67.08</v>
+      </c>
+      <c r="F28" t="n">
+        <v>57.78</v>
+      </c>
       <c r="G28" t="n">
-        <v>4.2</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="29">
@@ -932,14 +1148,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+        <v>52.27</v>
+      </c>
+      <c r="C29" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="D29" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="E29" t="n">
+        <v>68.02</v>
+      </c>
+      <c r="F29" t="n">
+        <v>57.36</v>
+      </c>
       <c r="G29" t="n">
-        <v>4.18</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="30">
@@ -949,14 +1173,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+        <v>52.59</v>
+      </c>
+      <c r="C30" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="D30" t="n">
+        <v>59.41</v>
+      </c>
+      <c r="E30" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="F30" t="n">
+        <v>56.94</v>
+      </c>
       <c r="G30" t="n">
-        <v>4.04</v>
+        <v>15.28</v>
       </c>
     </row>
     <row r="31">
@@ -966,14 +1198,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+        <v>52.54</v>
+      </c>
+      <c r="C31" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="D31" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="E31" t="n">
+        <v>67.86</v>
+      </c>
+      <c r="F31" t="n">
+        <v>56.52</v>
+      </c>
       <c r="G31" t="n">
-        <v>4.14</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="32">
@@ -983,14 +1223,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+        <v>52.37</v>
+      </c>
+      <c r="C32" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="D32" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="F32" t="n">
+        <v>56.1</v>
+      </c>
       <c r="G32" t="n">
-        <v>4.29</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="33">
@@ -1000,14 +1248,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+        <v>52.27</v>
+      </c>
+      <c r="C33" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="D33" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="E33" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="F33" t="n">
+        <v>55.68</v>
+      </c>
       <c r="G33" t="n">
-        <v>4.21</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="34">
@@ -1017,14 +1273,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+        <v>52.31</v>
+      </c>
+      <c r="C34" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="D34" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="E34" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="F34" t="n">
+        <v>55.26</v>
+      </c>
       <c r="G34" t="n">
-        <v>4.56</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="35">
@@ -1034,14 +1298,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+        <v>52.66</v>
+      </c>
+      <c r="C35" t="n">
+        <v>59.09</v>
+      </c>
+      <c r="D35" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="E35" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="F35" t="n">
+        <v>54.84</v>
+      </c>
       <c r="G35" t="n">
-        <v>4.81</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="36">
@@ -1051,14 +1323,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+        <v>53.07</v>
+      </c>
+      <c r="C36" t="n">
+        <v>59.89</v>
+      </c>
+      <c r="D36" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="E36" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="F36" t="n">
+        <v>54.42</v>
+      </c>
       <c r="G36" t="n">
-        <v>4.93</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="37">
@@ -1068,14 +1348,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+        <v>53.46</v>
+      </c>
+      <c r="C37" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58.91</v>
+      </c>
+      <c r="E37" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="F37" t="n">
+        <v>54</v>
+      </c>
       <c r="G37" t="n">
-        <v>5.54</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="38">
@@ -1085,14 +1373,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+        <v>53.27</v>
+      </c>
+      <c r="C38" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="D38" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="E38" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="F38" t="n">
+        <v>53.69</v>
+      </c>
       <c r="G38" t="n">
-        <v>4.39</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="39">
@@ -1102,14 +1398,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+        <v>53.11</v>
+      </c>
+      <c r="C39" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="D39" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="E39" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="F39" t="n">
+        <v>53.38</v>
+      </c>
       <c r="G39" t="n">
-        <v>4.69</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="40">
@@ -1119,22 +1423,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>52.18</v>
+        <v>52.88</v>
       </c>
       <c r="C40" t="n">
-        <v>37.98</v>
+        <v>55.9</v>
       </c>
       <c r="D40" t="n">
-        <v>77.14</v>
+        <v>59.92</v>
       </c>
       <c r="E40" t="n">
         <v>67.77</v>
       </c>
       <c r="F40" t="n">
-        <v>50.32</v>
+        <v>53.08</v>
       </c>
       <c r="G40" t="n">
-        <v>28.36</v>
+        <v>17.42</v>
       </c>
     </row>
     <row r="41">
@@ -1144,22 +1448,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>52.26</v>
+        <v>52.63</v>
       </c>
       <c r="C41" t="n">
-        <v>37.98</v>
+        <v>54.2</v>
       </c>
       <c r="D41" t="n">
-        <v>77.39</v>
+        <v>60.31</v>
       </c>
       <c r="E41" t="n">
         <v>67.77</v>
       </c>
       <c r="F41" t="n">
-        <v>50.32</v>
+        <v>52.77</v>
       </c>
       <c r="G41" t="n">
-        <v>28.55</v>
+        <v>18.89</v>
       </c>
     </row>
     <row r="42">
@@ -1169,22 +1473,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>52.61</v>
+        <v>52.37</v>
       </c>
       <c r="C42" t="n">
-        <v>37.98</v>
+        <v>53.13</v>
       </c>
       <c r="D42" t="n">
-        <v>79.40000000000001</v>
+        <v>60.31</v>
       </c>
       <c r="E42" t="n">
         <v>67.77</v>
       </c>
       <c r="F42" t="n">
-        <v>50.32</v>
+        <v>52.46</v>
       </c>
       <c r="G42" t="n">
-        <v>28.24</v>
+        <v>19.61</v>
       </c>
     </row>
     <row r="43">
@@ -1194,22 +1498,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>52.75</v>
+        <v>52.38</v>
       </c>
       <c r="C43" t="n">
-        <v>37.98</v>
+        <v>52.45</v>
       </c>
       <c r="D43" t="n">
-        <v>81.22</v>
+        <v>61.31</v>
       </c>
       <c r="E43" t="n">
         <v>67.77</v>
       </c>
       <c r="F43" t="n">
-        <v>50.32</v>
+        <v>52.16</v>
       </c>
       <c r="G43" t="n">
-        <v>26.72</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
@@ -1219,22 +1523,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>52.51</v>
+        <v>52.24</v>
       </c>
       <c r="C44" t="n">
-        <v>37.98</v>
+        <v>51.06</v>
       </c>
       <c r="D44" t="n">
-        <v>81.12</v>
+        <v>62.8</v>
       </c>
       <c r="E44" t="n">
         <v>67.77</v>
       </c>
       <c r="F44" t="n">
-        <v>50.32</v>
+        <v>51.85</v>
       </c>
       <c r="G44" t="n">
-        <v>25.26</v>
+        <v>20.21</v>
       </c>
     </row>
     <row r="45">
@@ -1244,22 +1548,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>49.91</v>
+        <v>52.15</v>
       </c>
       <c r="C45" t="n">
-        <v>42.76</v>
+        <v>49.4</v>
       </c>
       <c r="D45" t="n">
-        <v>60.75</v>
+        <v>64.3</v>
       </c>
       <c r="E45" t="n">
         <v>67.77</v>
       </c>
       <c r="F45" t="n">
-        <v>50.32</v>
+        <v>51.54</v>
       </c>
       <c r="G45" t="n">
-        <v>25.57</v>
+        <v>21.26</v>
       </c>
     </row>
     <row r="46">
@@ -1269,22 +1573,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>49.47</v>
+        <v>51.68</v>
       </c>
       <c r="C46" t="n">
-        <v>41.07</v>
+        <v>47.28</v>
       </c>
       <c r="D46" t="n">
-        <v>60.77</v>
+        <v>64.66</v>
       </c>
       <c r="E46" t="n">
         <v>67.77</v>
       </c>
       <c r="F46" t="n">
-        <v>50.32</v>
+        <v>51.24</v>
       </c>
       <c r="G46" t="n">
-        <v>25.92</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="47">
@@ -1294,22 +1598,22 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>49.74</v>
+        <v>51.16</v>
       </c>
       <c r="C47" t="n">
-        <v>41.92</v>
+        <v>45.25</v>
       </c>
       <c r="D47" t="n">
-        <v>60.68</v>
+        <v>64.92</v>
       </c>
       <c r="E47" t="n">
         <v>67.77</v>
       </c>
       <c r="F47" t="n">
-        <v>50.32</v>
+        <v>50.93</v>
       </c>
       <c r="G47" t="n">
-        <v>26.2</v>
+        <v>22.74</v>
       </c>
     </row>
     <row r="48">
@@ -1319,22 +1623,22 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>49.68</v>
+        <v>50.35</v>
       </c>
       <c r="C48" t="n">
-        <v>41.6</v>
+        <v>43.02</v>
       </c>
       <c r="D48" t="n">
-        <v>60.59</v>
+        <v>64.06</v>
       </c>
       <c r="E48" t="n">
         <v>67.77</v>
       </c>
       <c r="F48" t="n">
-        <v>50.32</v>
+        <v>50.62</v>
       </c>
       <c r="G48" t="n">
-        <v>26.51</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="49">
@@ -1344,13 +1648,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>49.41</v>
+        <v>49.82</v>
       </c>
       <c r="C49" t="n">
-        <v>40.29</v>
+        <v>41.03</v>
       </c>
       <c r="D49" t="n">
-        <v>61.36</v>
+        <v>64.81</v>
       </c>
       <c r="E49" t="n">
         <v>67.77</v>
@@ -1359,7 +1663,7 @@
         <v>50.32</v>
       </c>
       <c r="G49" t="n">
-        <v>26.3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50">
@@ -1369,13 +1673,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>50.14</v>
+        <v>50.69</v>
       </c>
       <c r="C50" t="n">
-        <v>41.06</v>
+        <v>42.11</v>
       </c>
       <c r="D50" t="n">
-        <v>62.24</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E50" t="n">
         <v>67.77</v>
@@ -1384,7 +1688,7 @@
         <v>52.65</v>
       </c>
       <c r="G50" t="n">
-        <v>26.13</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="51">
@@ -1394,13 +1698,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>50.81</v>
+        <v>51.47</v>
       </c>
       <c r="C51" t="n">
-        <v>41.87</v>
+        <v>43.03</v>
       </c>
       <c r="D51" t="n">
-        <v>62.76</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="E51" t="n">
         <v>67.77</v>
@@ -1409,7 +1713,7 @@
         <v>54.98</v>
       </c>
       <c r="G51" t="n">
-        <v>25.95</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="52">
@@ -1419,13 +1723,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>47.32</v>
+        <v>47.94</v>
       </c>
       <c r="C52" t="n">
-        <v>42.82</v>
+        <v>44.04</v>
       </c>
       <c r="D52" t="n">
-        <v>62.39</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="E52" t="n">
         <v>47.38</v>
@@ -1434,7 +1738,7 @@
         <v>57.31</v>
       </c>
       <c r="G52" t="n">
-        <v>26.15</v>
+        <v>22.94</v>
       </c>
     </row>
     <row r="53">
@@ -1444,13 +1748,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>47.79</v>
+        <v>48.3</v>
       </c>
       <c r="C53" t="n">
-        <v>43.72</v>
+        <v>44.8</v>
       </c>
       <c r="D53" t="n">
-        <v>62.22</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="E53" t="n">
         <v>46.63</v>
@@ -1459,7 +1763,7 @@
         <v>59.65</v>
       </c>
       <c r="G53" t="n">
-        <v>26.36</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="54">
@@ -1469,13 +1773,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>48.22</v>
+        <v>48.38</v>
       </c>
       <c r="C54" t="n">
-        <v>44.03</v>
+        <v>44.19</v>
       </c>
       <c r="D54" t="n">
-        <v>62.08</v>
+        <v>64.94</v>
       </c>
       <c r="E54" t="n">
         <v>45.88</v>
@@ -1484,7 +1788,7 @@
         <v>61.98</v>
       </c>
       <c r="G54" t="n">
-        <v>27.46</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="55">
@@ -1494,13 +1798,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>48.41</v>
+        <v>48.27</v>
       </c>
       <c r="C55" t="n">
-        <v>43.56</v>
+        <v>43.41</v>
       </c>
       <c r="D55" t="n">
-        <v>61.41</v>
+        <v>63.12</v>
       </c>
       <c r="E55" t="n">
         <v>45.13</v>
@@ -1509,7 +1813,7 @@
         <v>64.31</v>
       </c>
       <c r="G55" t="n">
-        <v>29.27</v>
+        <v>26.35</v>
       </c>
     </row>
     <row r="56">
@@ -1519,13 +1823,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>48.96</v>
+        <v>48.66</v>
       </c>
       <c r="C56" t="n">
-        <v>42.75</v>
+        <v>42.71</v>
       </c>
       <c r="D56" t="n">
-        <v>60.79</v>
+        <v>61.52</v>
       </c>
       <c r="E56" t="n">
         <v>44.38</v>
@@ -1534,7 +1838,7 @@
         <v>66.64</v>
       </c>
       <c r="G56" t="n">
-        <v>34.02</v>
+        <v>31.15</v>
       </c>
     </row>
     <row r="57">
@@ -1544,13 +1848,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>49.48</v>
+        <v>48.99</v>
       </c>
       <c r="C57" t="n">
-        <v>42.36</v>
+        <v>42.11</v>
       </c>
       <c r="D57" t="n">
-        <v>59.68</v>
+        <v>59.66</v>
       </c>
       <c r="E57" t="n">
         <v>43.63</v>
@@ -1559,7 +1863,7 @@
         <v>68.97</v>
       </c>
       <c r="G57" t="n">
-        <v>38.44</v>
+        <v>35.65</v>
       </c>
     </row>
     <row r="58">
@@ -1569,13 +1873,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>50.38</v>
+        <v>49.79</v>
       </c>
       <c r="C58" t="n">
-        <v>43</v>
+        <v>42.54</v>
       </c>
       <c r="D58" t="n">
-        <v>59.11</v>
+        <v>58.91</v>
       </c>
       <c r="E58" t="n">
         <v>42.88</v>
@@ -1584,7 +1888,7 @@
         <v>71.3</v>
       </c>
       <c r="G58" t="n">
-        <v>42.59</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="59">
@@ -1594,13 +1898,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>51.2</v>
+        <v>50.64</v>
       </c>
       <c r="C59" t="n">
-        <v>43.46</v>
+        <v>43.2</v>
       </c>
       <c r="D59" t="n">
-        <v>58.58</v>
+        <v>58.21</v>
       </c>
       <c r="E59" t="n">
         <v>42.13</v>
@@ -1609,7 +1913,7 @@
         <v>73.64</v>
       </c>
       <c r="G59" t="n">
-        <v>46.46</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="60">
@@ -1619,7 +1923,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>51.93</v>
+        <v>51.53</v>
       </c>
       <c r="C60" t="n">
         <v>43.85</v>
@@ -1634,7 +1938,7 @@
         <v>75.97</v>
       </c>
       <c r="G60" t="n">
-        <v>49.59</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="61">
@@ -1644,7 +1948,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52.24</v>
+        <v>51.87</v>
       </c>
       <c r="C61" t="n">
         <v>43.68</v>
@@ -1659,7 +1963,7 @@
         <v>78.3</v>
       </c>
       <c r="G61" t="n">
-        <v>52.89</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="62">
@@ -1669,7 +1973,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>52.28</v>
+        <v>51.92</v>
       </c>
       <c r="C62" t="n">
         <v>43.57</v>
@@ -1684,7 +1988,7 @@
         <v>79.06</v>
       </c>
       <c r="G62" t="n">
-        <v>55.9</v>
+        <v>53.52</v>
       </c>
     </row>
     <row r="63">
@@ -1694,7 +1998,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>52.4</v>
+        <v>52.06</v>
       </c>
       <c r="C63" t="n">
         <v>43.68</v>
@@ -1709,7 +2013,7 @@
         <v>79.81</v>
       </c>
       <c r="G63" t="n">
-        <v>58.95</v>
+        <v>56.68</v>
       </c>
     </row>
     <row r="64">
@@ -1719,7 +2023,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>52.65</v>
+        <v>52.31</v>
       </c>
       <c r="C64" t="n">
         <v>44.04</v>
@@ -1734,7 +2038,7 @@
         <v>80.56999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>61.19</v>
+        <v>58.96</v>
       </c>
     </row>
     <row r="65">
@@ -1744,7 +2048,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>53.19</v>
+        <v>52.87</v>
       </c>
       <c r="C65" t="n">
         <v>44.62</v>
@@ -1759,7 +2063,7 @@
         <v>81.31999999999999</v>
       </c>
       <c r="G65" t="n">
-        <v>63.18</v>
+        <v>61.02</v>
       </c>
     </row>
     <row r="66">
@@ -1769,7 +2073,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>53.59</v>
+        <v>53.27</v>
       </c>
       <c r="C66" t="n">
         <v>45.78</v>
@@ -1784,7 +2088,7 @@
         <v>82.08</v>
       </c>
       <c r="G66" t="n">
-        <v>63.7</v>
+        <v>61.58</v>
       </c>
     </row>
     <row r="67">
@@ -1794,7 +2098,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>54.13</v>
+        <v>53.82</v>
       </c>
       <c r="C67" t="n">
         <v>46.67</v>
@@ -1809,7 +2113,7 @@
         <v>82.83</v>
       </c>
       <c r="G67" t="n">
-        <v>64.16</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="68">
@@ -1819,7 +2123,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>54.82</v>
+        <v>54.52</v>
       </c>
       <c r="C68" t="n">
         <v>48.02</v>
@@ -1834,7 +2138,7 @@
         <v>83.59</v>
       </c>
       <c r="G68" t="n">
-        <v>64.75</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="69">
@@ -1844,7 +2148,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>55.76</v>
+        <v>55.49</v>
       </c>
       <c r="C69" t="n">
         <v>49.57</v>
@@ -1859,7 +2163,7 @@
         <v>84.34999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>65.39</v>
+        <v>63.54</v>
       </c>
     </row>
     <row r="70">
@@ -1869,7 +2173,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>56.05</v>
+        <v>55.79</v>
       </c>
       <c r="C70" t="n">
         <v>49.74</v>
@@ -1884,7 +2188,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>66.01000000000001</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -1894,7 +2198,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>55.55</v>
+        <v>55.3</v>
       </c>
       <c r="C71" t="n">
         <v>47.39</v>
@@ -1909,7 +2213,7 @@
         <v>85.86</v>
       </c>
       <c r="G71" t="n">
-        <v>66.48999999999999</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="72">
@@ -1919,7 +2223,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>54.98</v>
+        <v>54.73</v>
       </c>
       <c r="C72" t="n">
         <v>45.04</v>
@@ -1934,7 +2238,7 @@
         <v>86.61</v>
       </c>
       <c r="G72" t="n">
-        <v>66.95999999999999</v>
+        <v>65.31999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -1944,7 +2248,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>54.49</v>
+        <v>54.25</v>
       </c>
       <c r="C73" t="n">
         <v>42.71</v>
@@ -1959,7 +2263,7 @@
         <v>87.37</v>
       </c>
       <c r="G73" t="n">
-        <v>67.13</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="74">
@@ -1969,10 +2273,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>54.09</v>
+        <v>53.85</v>
       </c>
       <c r="C74" t="n">
-        <v>40.9</v>
+        <v>40.91</v>
       </c>
       <c r="D74" t="n">
         <v>56.93</v>
@@ -1981,10 +2285,10 @@
         <v>36.09</v>
       </c>
       <c r="F74" t="n">
-        <v>87.38</v>
+        <v>87.37</v>
       </c>
       <c r="G74" t="n">
-        <v>67.39</v>
+        <v>65.79000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -1994,10 +2298,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>53.75</v>
+        <v>53.52</v>
       </c>
       <c r="C75" t="n">
-        <v>39.25</v>
+        <v>39.28</v>
       </c>
       <c r="D75" t="n">
         <v>57.49</v>
@@ -2006,10 +2310,10 @@
         <v>36.09</v>
       </c>
       <c r="F75" t="n">
-        <v>87.39</v>
+        <v>87.38</v>
       </c>
       <c r="G75" t="n">
-        <v>67.68000000000001</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -2019,10 +2323,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>52.99</v>
+        <v>52.78</v>
       </c>
       <c r="C76" t="n">
-        <v>37.2</v>
+        <v>37.25</v>
       </c>
       <c r="D76" t="n">
         <v>56.54</v>
@@ -2031,10 +2335,10 @@
         <v>36.09</v>
       </c>
       <c r="F76" t="n">
-        <v>87.39</v>
+        <v>87.38</v>
       </c>
       <c r="G76" t="n">
-        <v>68</v>
+        <v>66.45999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -2044,10 +2348,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>52.09</v>
+        <v>51.89</v>
       </c>
       <c r="C77" t="n">
-        <v>35.41</v>
+        <v>35.48</v>
       </c>
       <c r="D77" t="n">
         <v>54.53</v>
@@ -2056,10 +2360,10 @@
         <v>36.09</v>
       </c>
       <c r="F77" t="n">
-        <v>87.40000000000001</v>
+        <v>87.39</v>
       </c>
       <c r="G77" t="n">
-        <v>68.26000000000001</v>
+        <v>66.73999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -2069,10 +2373,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>51.24</v>
+        <v>51.04</v>
       </c>
       <c r="C78" t="n">
-        <v>33.36</v>
+        <v>33.45</v>
       </c>
       <c r="D78" t="n">
         <v>53.23</v>
@@ -2081,10 +2385,10 @@
         <v>36.09</v>
       </c>
       <c r="F78" t="n">
-        <v>87.41</v>
+        <v>87.39</v>
       </c>
       <c r="G78" t="n">
-        <v>68.38</v>
+        <v>66.89</v>
       </c>
     </row>
     <row r="79">
@@ -2094,10 +2398,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>50.44</v>
+        <v>50.24</v>
       </c>
       <c r="C79" t="n">
-        <v>32.54</v>
+        <v>32.65</v>
       </c>
       <c r="D79" t="n">
         <v>51.26</v>
@@ -2106,10 +2410,10 @@
         <v>35.29</v>
       </c>
       <c r="F79" t="n">
-        <v>87.42</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>68.36</v>
+        <v>66.86</v>
       </c>
     </row>
     <row r="80">
@@ -2119,10 +2423,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>49.7</v>
+        <v>49.51</v>
       </c>
       <c r="C80" t="n">
-        <v>31.66</v>
+        <v>31.79</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -2131,10 +2435,35 @@
         <v>34.5</v>
       </c>
       <c r="F80" t="n">
-        <v>87.43000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>68.33</v>
+        <v>66.81</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="C81" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="D81" t="n">
+        <v>48.04</v>
+      </c>
+      <c r="E81" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="F81" t="n">
+        <v>87.41</v>
+      </c>
+      <c r="G81" t="n">
+        <v>66.70999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2202,14 +2531,20 @@
         <v>2003</v>
       </c>
       <c r="B2" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+        <v>49.3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.3</v>
+      </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>82.3</v>
+      </c>
       <c r="G2" t="n">
-        <v>41.9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -2217,14 +2552,20 @@
         <v>2004</v>
       </c>
       <c r="B3" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+        <v>63.1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3" t="n">
+        <v>58.3</v>
+      </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>65.2</v>
+      </c>
       <c r="G3" t="n">
-        <v>44.8</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="4">
@@ -2232,14 +2573,20 @@
         <v>2005</v>
       </c>
       <c r="B4" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+        <v>60.9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>52.1</v>
+      </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>70.3</v>
+      </c>
       <c r="G4" t="n">
-        <v>43.1</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="5">
@@ -2247,12 +2594,18 @@
         <v>2006</v>
       </c>
       <c r="B5" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+        <v>54.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50.8</v>
+      </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>35.2</v>
+      </c>
       <c r="G5" t="n">
         <v>55.6</v>
       </c>
@@ -2262,14 +2615,20 @@
         <v>2007</v>
       </c>
       <c r="B6" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+        <v>71.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>61</v>
+      </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>62.5</v>
+      </c>
       <c r="G6" t="n">
-        <v>60.7</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="7">
@@ -2277,14 +2636,20 @@
         <v>2008</v>
       </c>
       <c r="B7" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+        <v>73.59999999999999</v>
+      </c>
+      <c r="C7" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>54.3</v>
+      </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>65.90000000000001</v>
+      </c>
       <c r="G7" t="n">
-        <v>61.7</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="8">
@@ -2292,14 +2657,20 @@
         <v>2009</v>
       </c>
       <c r="B8" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+        <v>66.40000000000001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>41.2</v>
+      </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>48.8</v>
+      </c>
       <c r="G8" t="n">
-        <v>51.4</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="9">
@@ -2307,14 +2678,20 @@
         <v>2010</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+        <v>63.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>50.1</v>
+      </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>28.3</v>
+      </c>
       <c r="G9" t="n">
-        <v>43</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="10">
@@ -2322,14 +2699,20 @@
         <v>2011</v>
       </c>
       <c r="B10" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+        <v>58.9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>44.8</v>
+      </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>22.4</v>
+      </c>
       <c r="G10" t="n">
-        <v>42.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="11">
@@ -2337,14 +2720,20 @@
         <v>2012</v>
       </c>
       <c r="B11" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+        <v>57.9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>91</v>
+      </c>
+      <c r="D11" t="n">
+        <v>46.8</v>
+      </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>23.7</v>
+      </c>
       <c r="G11" t="n">
-        <v>30.7</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="12">
@@ -2352,14 +2741,20 @@
         <v>2013</v>
       </c>
       <c r="B12" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+        <v>55.8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>95</v>
+      </c>
+      <c r="D12" t="n">
+        <v>45.6</v>
+      </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>23.6</v>
+      </c>
       <c r="G12" t="n">
-        <v>19.6</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="13">
@@ -2367,14 +2762,20 @@
         <v>2014</v>
       </c>
       <c r="B13" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+        <v>58.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>65</v>
+      </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>29.1</v>
+      </c>
       <c r="G13" t="n">
-        <v>16.1</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="14">
@@ -2382,14 +2783,20 @@
         <v>2015</v>
       </c>
       <c r="B14" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+        <v>66.7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>91.59999999999999</v>
+      </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G14" t="n">
-        <v>11.8</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="15">
@@ -2397,12 +2804,18 @@
         <v>2016</v>
       </c>
       <c r="B15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+        <v>56.9</v>
+      </c>
+      <c r="C15" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>60.7</v>
+      </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>44.6</v>
+      </c>
       <c r="G15" t="n">
         <v>9.6</v>
       </c>
@@ -2412,14 +2825,22 @@
         <v>2017</v>
       </c>
       <c r="B16" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+        <v>61.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E16" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>33.6</v>
+      </c>
       <c r="G16" t="n">
-        <v>13.8</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="17">
@@ -2427,14 +2848,22 @@
         <v>2018</v>
       </c>
       <c r="B17" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+        <v>66.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>46.1</v>
+      </c>
       <c r="G17" t="n">
-        <v>15.4</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="18">
@@ -2442,14 +2871,22 @@
         <v>2019</v>
       </c>
       <c r="B18" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+        <v>70.40000000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>94</v>
+      </c>
+      <c r="E18" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>58</v>
+      </c>
       <c r="G18" t="n">
-        <v>24.4</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="19">
@@ -2457,14 +2894,22 @@
         <v>2020</v>
       </c>
       <c r="B19" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+        <v>42.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>17</v>
+      </c>
+      <c r="D19" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>68.40000000000001</v>
+      </c>
       <c r="G19" t="n">
-        <v>6.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="20">
@@ -2472,14 +2917,22 @@
         <v>2021</v>
       </c>
       <c r="B20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+        <v>50.4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>59</v>
+      </c>
       <c r="G20" t="n">
-        <v>4.4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -2487,14 +2940,22 @@
         <v>2022</v>
       </c>
       <c r="B21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+        <v>53.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>54</v>
+      </c>
       <c r="G21" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="22">
@@ -2502,13 +2963,13 @@
         <v>2023</v>
       </c>
       <c r="B22" t="n">
-        <v>48.9</v>
+        <v>49.8</v>
       </c>
       <c r="C22" t="n">
-        <v>40.3</v>
+        <v>41</v>
       </c>
       <c r="D22" t="n">
-        <v>61.4</v>
+        <v>64.8</v>
       </c>
       <c r="E22" t="n">
         <v>67.8</v>
@@ -2571,22 +3032,22 @@
         <v>2026</v>
       </c>
       <c r="B25" t="n">
-        <v>48.1</v>
+        <v>49.1</v>
       </c>
       <c r="C25" t="n">
-        <v>30</v>
+        <v>31.3</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>48.3</v>
       </c>
       <c r="E25" t="n">
-        <v>33.5</v>
+        <v>34.1</v>
       </c>
       <c r="F25" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>67.2</v>
+        <v>67.3</v>
       </c>
     </row>
   </sheetData>
